--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.34002514765988</v>
+        <v>8.180254086494731</v>
       </c>
       <c r="D2" t="n">
-        <v>33.64367024130153</v>
+        <v>5.467096414211499</v>
       </c>
       <c r="E2" t="n">
-        <v>11.63517866964423</v>
+        <v>1.890716533817188</v>
       </c>
       <c r="F2" t="n">
-        <v>11.04602744662929</v>
+        <v>1.794979460077259</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.77926957688031</v>
+        <v>6.464131306243051</v>
       </c>
       <c r="D3" t="n">
-        <v>31.93412121256326</v>
+        <v>5.189294697041531</v>
       </c>
       <c r="E3" t="n">
-        <v>11.63517866964423</v>
+        <v>1.890716533817188</v>
       </c>
       <c r="F3" t="n">
-        <v>11.04602744662929</v>
+        <v>1.794979460077259</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.52979298662007</v>
+        <v>8.211091360325762</v>
       </c>
       <c r="D4" t="n">
-        <v>35.07439097212209</v>
+        <v>5.699588532969839</v>
       </c>
       <c r="E4" t="n">
-        <v>11.63517866964423</v>
+        <v>1.890716533817188</v>
       </c>
       <c r="F4" t="n">
-        <v>11.04602744662929</v>
+        <v>1.794979460077259</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.32907241091275</v>
+        <v>8.340974266773323</v>
       </c>
       <c r="D5" t="n">
-        <v>7.471160991572344</v>
+        <v>1.214063661130506</v>
       </c>
       <c r="E5" t="n">
-        <v>11.63517866964423</v>
+        <v>1.890716533817188</v>
       </c>
       <c r="F5" t="n">
-        <v>11.04602744662929</v>
+        <v>1.794979460077259</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>61.1833833873897</v>
+        <v>9.942299800450828</v>
       </c>
       <c r="D6" t="n">
-        <v>15.11746469198483</v>
+        <v>2.456588012447535</v>
       </c>
       <c r="E6" t="n">
-        <v>11.63517866964423</v>
+        <v>1.890716533817188</v>
       </c>
       <c r="F6" t="n">
-        <v>11.04602744662929</v>
+        <v>1.794979460077259</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.87419111785721</v>
+        <v>7.454556056651796</v>
       </c>
       <c r="D7" t="n">
-        <v>29.38643394493452</v>
+        <v>4.775295516051861</v>
       </c>
       <c r="E7" t="n">
-        <v>11.63517866964423</v>
+        <v>1.890716533817188</v>
       </c>
       <c r="F7" t="n">
-        <v>11.04602744662929</v>
+        <v>1.794979460077259</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.70884086983293</v>
+        <v>4.665186641347851</v>
       </c>
       <c r="D8" t="n">
-        <v>29.97136722312805</v>
+        <v>4.870347173758308</v>
       </c>
       <c r="E8" t="n">
-        <v>11.63517866964423</v>
+        <v>1.890716533817188</v>
       </c>
       <c r="F8" t="n">
-        <v>11.04602744662929</v>
+        <v>1.794979460077259</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>56.50454347584512</v>
+        <v>9.181988314824832</v>
       </c>
       <c r="D9" t="n">
-        <v>34.91791422854495</v>
+        <v>5.674161062138555</v>
       </c>
       <c r="E9" t="n">
-        <v>11.63517866964423</v>
+        <v>1.890716533817188</v>
       </c>
       <c r="F9" t="n">
-        <v>11.04602744662929</v>
+        <v>1.794979460077259</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>51.61752896825393</v>
+        <v>8.387848457341263</v>
       </c>
       <c r="D10" t="n">
-        <v>43.78654558858663</v>
+        <v>7.115313658145327</v>
       </c>
       <c r="E10" t="n">
-        <v>11.63517866964423</v>
+        <v>1.890716533817188</v>
       </c>
       <c r="F10" t="n">
-        <v>11.04602744662929</v>
+        <v>1.794979460077259</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>20.21540362037716</v>
+        <v>3.285003088311289</v>
       </c>
       <c r="D11" t="n">
-        <v>9.438099521557911</v>
+        <v>1.533691172253161</v>
       </c>
       <c r="E11" t="n">
-        <v>11.63517866964423</v>
+        <v>1.890716533817188</v>
       </c>
       <c r="F11" t="n">
-        <v>11.04602744662929</v>
+        <v>1.794979460077259</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>38.34545718823222</v>
+        <v>6.231136793087735</v>
       </c>
       <c r="D12" t="n">
-        <v>31.59021852918299</v>
+        <v>5.133410510992237</v>
       </c>
       <c r="E12" t="n">
-        <v>11.63517866964423</v>
+        <v>1.890716533817188</v>
       </c>
       <c r="F12" t="n">
-        <v>11.04602744662929</v>
+        <v>1.794979460077259</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
